--- a/artfynd/A 36383-2024 artfynd.xlsx
+++ b/artfynd/A 36383-2024 artfynd.xlsx
@@ -4643,7 +4643,7 @@
         <v>119796482</v>
       </c>
       <c r="B41" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 36383-2024 artfynd.xlsx
+++ b/artfynd/A 36383-2024 artfynd.xlsx
@@ -1384,11 +1384,11 @@
         <v>119080324</v>
       </c>
       <c r="B9" t="n">
-        <v>56520</v>
+        <v>56593</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2196,11 +2196,11 @@
         <v>119080323</v>
       </c>
       <c r="B17" t="n">
-        <v>56520</v>
+        <v>56593</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4234,11 +4234,11 @@
         <v>119080347</v>
       </c>
       <c r="B37" t="n">
-        <v>56523</v>
+        <v>56596</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">

--- a/artfynd/A 36383-2024 artfynd.xlsx
+++ b/artfynd/A 36383-2024 artfynd.xlsx
@@ -1384,11 +1384,11 @@
         <v>119080324</v>
       </c>
       <c r="B9" t="n">
-        <v>56593</v>
+        <v>56520</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2196,11 +2196,11 @@
         <v>119080323</v>
       </c>
       <c r="B17" t="n">
-        <v>56593</v>
+        <v>56520</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">

--- a/artfynd/A 36383-2024 artfynd.xlsx
+++ b/artfynd/A 36383-2024 artfynd.xlsx
@@ -4234,7 +4234,7 @@
         <v>119080347</v>
       </c>
       <c r="B37" t="n">
-        <v>56596</v>
+        <v>56597</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 36383-2024 artfynd.xlsx
+++ b/artfynd/A 36383-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,35 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119080366</v>
+        <v>119080353</v>
       </c>
       <c r="B2" t="n">
-        <v>97809</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -711,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>816948</v>
+        <v>816903</v>
       </c>
       <c r="R2" t="n">
-        <v>7377639</v>
+        <v>7377540</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -773,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119080311</v>
+        <v>119080388</v>
       </c>
       <c r="B3" t="n">
-        <v>79113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -813,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>816891</v>
+        <v>816837</v>
       </c>
       <c r="R3" t="n">
-        <v>7377556</v>
+        <v>7377516</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,15 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119080394</v>
+        <v>119080390</v>
       </c>
       <c r="B4" t="n">
-        <v>82303</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>816871</v>
+        <v>816903</v>
       </c>
       <c r="R4" t="n">
-        <v>7377482</v>
+        <v>7377540</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,15 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119080381</v>
+        <v>119080391</v>
       </c>
       <c r="B5" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>816881</v>
+        <v>816933</v>
       </c>
       <c r="R5" t="n">
-        <v>7377484</v>
+        <v>7377526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,37 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119080332</v>
+        <v>119080392</v>
       </c>
       <c r="B6" t="n">
-        <v>97910</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1119,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>816852</v>
+        <v>816909</v>
       </c>
       <c r="R6" t="n">
-        <v>7377495</v>
+        <v>7377508</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,35 +1161,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119080365</v>
+        <v>119080393</v>
       </c>
       <c r="B7" t="n">
-        <v>97809</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1217,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>816912</v>
+        <v>816906</v>
       </c>
       <c r="R7" t="n">
-        <v>7377643</v>
+        <v>7377506</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,15 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119080393</v>
+        <v>119080394</v>
       </c>
       <c r="B8" t="n">
-        <v>82303</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>816906</v>
+        <v>816871</v>
       </c>
       <c r="R8" t="n">
-        <v>7377506</v>
+        <v>7377482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,50 +1355,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119080324</v>
+        <v>119796482</v>
       </c>
       <c r="B9" t="n">
-        <v>56520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Karkmyran, Nb</t>
+          <t>Dockasberg, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>816956</v>
+        <v>816923</v>
       </c>
       <c r="R9" t="n">
-        <v>7377634</v>
+        <v>7377600</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,12 +1424,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,49 +1449,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119080388</v>
+        <v>119080309</v>
       </c>
       <c r="B10" t="n">
-        <v>82303</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>816837</v>
+        <v>816867</v>
       </c>
       <c r="R10" t="n">
-        <v>7377516</v>
+        <v>7377482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,15 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119080360</v>
+        <v>119080310</v>
       </c>
       <c r="B11" t="n">
-        <v>97809</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,19 +1569,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1621,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>816991</v>
+        <v>816868</v>
       </c>
       <c r="R11" t="n">
-        <v>7377446</v>
+        <v>7377486</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,37 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119080334</v>
+        <v>119080370</v>
       </c>
       <c r="B12" t="n">
-        <v>97910</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1723,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>816849</v>
+        <v>816856</v>
       </c>
       <c r="R12" t="n">
-        <v>7377522</v>
+        <v>7377500</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,37 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119080312</v>
+        <v>119080371</v>
       </c>
       <c r="B13" t="n">
-        <v>79113</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1825,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>817111</v>
+        <v>816829</v>
       </c>
       <c r="R13" t="n">
-        <v>7377551</v>
+        <v>7377493</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,19 +1849,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119080377</v>
+        <v>119080372</v>
       </c>
       <c r="B14" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1927,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>816894</v>
+        <v>816831</v>
       </c>
       <c r="R14" t="n">
-        <v>7377564</v>
+        <v>7377505</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,19 +1946,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119080375</v>
+        <v>119080373</v>
       </c>
       <c r="B15" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2029,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>816854</v>
+        <v>816837</v>
       </c>
       <c r="R15" t="n">
-        <v>7377503</v>
+        <v>7377516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,37 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119080343</v>
+        <v>119080375</v>
       </c>
       <c r="B16" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2131,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>816896</v>
+        <v>816854</v>
       </c>
       <c r="R16" t="n">
-        <v>7377559</v>
+        <v>7377503</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,37 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119080323</v>
+        <v>119080376</v>
       </c>
       <c r="B17" t="n">
-        <v>56520</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2233,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>816915</v>
+        <v>816862</v>
       </c>
       <c r="R17" t="n">
-        <v>7377642</v>
+        <v>7377513</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2295,19 +2237,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119080373</v>
+        <v>119080377</v>
       </c>
       <c r="B18" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2335,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>816837</v>
+        <v>816894</v>
       </c>
       <c r="R18" t="n">
-        <v>7377516</v>
+        <v>7377564</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,37 +2334,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119080342</v>
+        <v>119080378</v>
       </c>
       <c r="B19" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>816856</v>
+        <v>816933</v>
       </c>
       <c r="R19" t="n">
-        <v>7377538</v>
+        <v>7377526</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2499,37 +2431,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119080341</v>
+        <v>119080379</v>
       </c>
       <c r="B20" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2539,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>816840</v>
+        <v>816916</v>
       </c>
       <c r="R20" t="n">
-        <v>7377508</v>
+        <v>7377524</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2601,35 +2528,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119080362</v>
+        <v>119080381</v>
       </c>
       <c r="B21" t="n">
-        <v>97809</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2637,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>817086</v>
+        <v>816881</v>
       </c>
       <c r="R21" t="n">
-        <v>7377456</v>
+        <v>7377484</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2699,37 +2625,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119080352</v>
+        <v>119080382</v>
       </c>
       <c r="B22" t="n">
-        <v>78260</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2739,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>817111</v>
+        <v>817122</v>
       </c>
       <c r="R22" t="n">
-        <v>7377551</v>
+        <v>7377460</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2801,15 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119080371</v>
+        <v>119080352</v>
       </c>
       <c r="B23" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2817,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2841,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>816829</v>
+        <v>817111</v>
       </c>
       <c r="R23" t="n">
-        <v>7377493</v>
+        <v>7377551</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,37 +2819,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119080379</v>
+        <v>119080340</v>
       </c>
       <c r="B24" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2943,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>816916</v>
+        <v>816835</v>
       </c>
       <c r="R24" t="n">
-        <v>7377524</v>
+        <v>7377515</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3005,15 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119080309</v>
+        <v>119080341</v>
       </c>
       <c r="B25" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3021,21 +2927,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3045,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>816867</v>
+        <v>816840</v>
       </c>
       <c r="R25" t="n">
-        <v>7377482</v>
+        <v>7377508</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3107,37 +3013,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119080376</v>
+        <v>119080342</v>
       </c>
       <c r="B26" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3147,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>816862</v>
+        <v>816856</v>
       </c>
       <c r="R26" t="n">
-        <v>7377513</v>
+        <v>7377538</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3209,37 +3110,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119080370</v>
+        <v>119080343</v>
       </c>
       <c r="B27" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3249,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>816856</v>
+        <v>816896</v>
       </c>
       <c r="R27" t="n">
-        <v>7377500</v>
+        <v>7377559</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,12 +3210,7 @@
         <v>119080315</v>
       </c>
       <c r="B28" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3418,37 +3309,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119080392</v>
+        <v>119080347</v>
       </c>
       <c r="B29" t="n">
-        <v>82303</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3458,7 +3344,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>816909</v>
+        <v>816868</v>
       </c>
       <c r="R29" t="n">
         <v>7377508</v>
@@ -3494,6 +3380,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3520,37 +3411,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119080391</v>
+        <v>119080332</v>
       </c>
       <c r="B30" t="n">
-        <v>82303</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3560,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>816933</v>
+        <v>816852</v>
       </c>
       <c r="R30" t="n">
-        <v>7377526</v>
+        <v>7377495</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3622,37 +3508,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119080378</v>
+        <v>119080334</v>
       </c>
       <c r="B31" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3662,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>816933</v>
+        <v>816849</v>
       </c>
       <c r="R31" t="n">
-        <v>7377526</v>
+        <v>7377522</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3724,39 +3605,30 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119080382</v>
+        <v>119080360</v>
       </c>
       <c r="B32" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3764,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>817122</v>
+        <v>816991</v>
       </c>
       <c r="R32" t="n">
-        <v>7377460</v>
+        <v>7377446</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3826,15 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119080310</v>
+        <v>119080362</v>
       </c>
       <c r="B33" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3842,23 +3709,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>223597</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3866,10 +3729,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>816868</v>
+        <v>817086</v>
       </c>
       <c r="R33" t="n">
-        <v>7377486</v>
+        <v>7377456</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3931,12 +3794,7 @@
         <v>119080363</v>
       </c>
       <c r="B34" t="n">
-        <v>97809</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4026,39 +3884,30 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119080390</v>
+        <v>119080364</v>
       </c>
       <c r="B35" t="n">
-        <v>82303</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>223597</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4066,10 +3915,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>816903</v>
+        <v>816971</v>
       </c>
       <c r="R35" t="n">
-        <v>7377540</v>
+        <v>7377527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4128,39 +3977,30 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119080353</v>
+        <v>119080365</v>
       </c>
       <c r="B36" t="n">
-        <v>78606</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>223597</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4168,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>816903</v>
+        <v>816912</v>
       </c>
       <c r="R36" t="n">
-        <v>7377540</v>
+        <v>7377643</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4212,7 +4052,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4231,15 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119080347</v>
+        <v>119080366</v>
       </c>
       <c r="B37" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4247,23 +4081,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102613</v>
+        <v>223597</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4271,10 +4101,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>816868</v>
+        <v>816948</v>
       </c>
       <c r="R37" t="n">
-        <v>7377508</v>
+        <v>7377639</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4307,11 +4137,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4338,15 +4163,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119080372</v>
+        <v>119080348</v>
       </c>
       <c r="B38" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4354,21 +4174,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4378,10 +4198,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>816831</v>
+        <v>817108</v>
       </c>
       <c r="R38" t="n">
-        <v>7377505</v>
+        <v>7377439</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4440,35 +4260,34 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119080364</v>
+        <v>119080311</v>
       </c>
       <c r="B39" t="n">
-        <v>97809</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>223597</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4476,10 +4295,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>816971</v>
+        <v>816891</v>
       </c>
       <c r="R39" t="n">
-        <v>7377527</v>
+        <v>7377556</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4538,15 +4357,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119080340</v>
+        <v>119080312</v>
       </c>
       <c r="B40" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4554,21 +4368,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4578,10 +4392,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>816835</v>
+        <v>817111</v>
       </c>
       <c r="R40" t="n">
-        <v>7377515</v>
+        <v>7377551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4637,117 +4451,6 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>119796482</v>
-      </c>
-      <c r="B41" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Dockasberg, Nb</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>816923</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7377600</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36383-2024 artfynd.xlsx
+++ b/artfynd/A 36383-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080353</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080388</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080390</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080391</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080392</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080393</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080394</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796482</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080309</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080310</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080370</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080371</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080372</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080373</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080375</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080376</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080377</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080378</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080379</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080381</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2719,6 +2824,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080382</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080352</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080340</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080341</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,6 +3232,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080342</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3204,6 +3334,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080343</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3306,6 +3441,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080315</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3408,6 +3548,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080347</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3505,6 +3650,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080332</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3602,6 +3752,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080334</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3695,6 +3850,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080360</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3788,6 +3948,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080362</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3881,6 +4046,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080363</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3974,6 +4144,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080364</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080365</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4160,6 +4340,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080366</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4257,6 +4442,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080348</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4354,6 +4544,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080311</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4451,8 +4646,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119080312</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>